--- a/output/2026-10-06_02_Croazia_Grad_Zagreb_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-06_02_Croazia_Grad_Zagreb_Depolverazione_Trattamento_aria.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Produttore/integratore di impianti di depolverazione, cabine di verniciatura, trasporto pneumatico; verificato via WebFetch sito ufficiale. Attenzione: più integratore/produttore diretto che puro distributore - valutare strategicamente</t>
+          <t>Produttore/integratore di impianti di depolverazione, cabine di verniciatura, trasporto pneumatico; verificato via WebFetch sito ufficiale. Attenzione: più integratore/produttore diretto che puro distributore - valutare strategicamente [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Filtration Group Industrial per filtrazione aria industriale/air pollution control. Email/telefono di contatto diretto (non generico aziendale); verificato via WebFetch sito ufficiale</t>
+          <t>Distributore ufficiale Filtration Group Industrial per filtrazione aria industriale/air pollution control. Email/telefono di contatto diretto (non generico aziendale); verificato via WebFetch sito ufficiale [DUPLICATO — vedi anche: 2026-10-05_20_Croazia_Međimurska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore macchine/utensili industriali, include aspiratori/dust collector a marchio Fervi. Nota geografica: Samobor è in Zagrebacka zupanija, non nel Grad Zagreb in senso stretto</t>
+          <t>Distributore macchine/utensili industriali, include aspiratori/dust collector a marchio Fervi. Nota geografica: Samobor è in Zagrebacka zupanija, non nel Grad Zagreb in senso stretto [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
